--- a/data/trans_orig/Q20C_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q20C_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2007</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2007 (tasa de respuesta: 96,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>38,41%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>60,87%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>947</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,59%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,15%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2455,47 +2455,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>19,42%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5760</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5100</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>20,19%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>790</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,26%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,51%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>846</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>59,11%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>60,56%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>61,49%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>26193</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,12 +4914,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>20247</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>31956</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>29243</t>
+          <t>29500</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>47277</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2012</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2012 (tasa de respuesta: 97,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5590,12 +5590,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,95%</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>58,7%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6335,77 +6335,77 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3048</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4955</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>61,52%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>4894</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1911</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>7736</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>51,3%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>20,03%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>81,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3048</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4955</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>61,52%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>4894</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1946</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>7704</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>51,3%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>20,4%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>80,76%</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>906</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6743,12 +6743,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>867</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>46,41%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21066</t>
+          <t>20524</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -7340,12 +7340,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12901</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17154</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -8135,47 +8135,47 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>2181</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>8298</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>56,51%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>23,48%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>89,34%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>5293</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
           <t>2073</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>8248</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>56,51%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>22,32%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>88,8%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>5293</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>2056</t>
-        </is>
-      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14908</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,49%</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8365,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,18%</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>58,2%</t>
         </is>
       </c>
     </row>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,15%</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>30653</t>
+          <t>30731</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>45776</t>
+          <t>44475</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>22269</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>37139</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>22331</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>41296</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>38531</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>39277</t>
+          <t>40272</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>63987</t>
+          <t>64152</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2016</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2016 (tasa de respuesta: 92,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10435,12 +10435,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10876,12 +10876,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10891,12 +10891,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,64%</t>
         </is>
       </c>
     </row>
@@ -10989,12 +10989,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,3%</t>
         </is>
       </c>
     </row>
@@ -11445,12 +11445,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11460,12 +11460,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -11558,12 +11558,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>847</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11573,12 +11573,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10910</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11643,12 +11643,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>62,3%</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>9880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -12014,12 +12014,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12029,12 +12029,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12049,12 +12049,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12064,12 +12064,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>14606</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12099,12 +12099,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>65,11%</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12177,12 +12177,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12212,12 +12212,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11349</t>
+          <t>11410</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12633,12 +12633,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12653,12 +12653,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12668,12 +12668,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>48,29%</t>
         </is>
       </c>
     </row>
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12711,12 +12711,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12766,12 +12766,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12781,12 +12781,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>47,35%</t>
         </is>
       </c>
     </row>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12859,12 +12859,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12894,12 +12894,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12972,12 +12972,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13007,12 +13007,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -13157,7 +13157,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13187,12 +13187,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>866</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13202,12 +13202,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13222,12 +13222,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13237,12 +13237,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>45,98%</t>
         </is>
       </c>
     </row>
@@ -13270,7 +13270,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13300,12 +13300,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13315,12 +13315,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13335,12 +13335,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13350,12 +13350,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>46,34%</t>
         </is>
       </c>
     </row>
@@ -13378,12 +13378,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13393,12 +13393,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13448,12 +13448,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13463,12 +13463,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -13496,7 +13496,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13541,12 +13541,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>11010</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13576,12 +13576,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,65%</t>
         </is>
       </c>
     </row>
@@ -13726,7 +13726,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13771,12 +13771,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13889,7 +13889,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>703</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13919,12 +13919,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,74%</t>
         </is>
       </c>
     </row>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13997,12 +13997,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -14130,12 +14130,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14145,12 +14145,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -14290,12 +14290,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14305,12 +14305,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>37453</t>
+          <t>38315</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14375,12 +14375,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -14403,12 +14403,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14418,12 +14418,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14453,12 +14453,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14488,12 +14488,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -14516,12 +14516,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14531,12 +14531,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14551,12 +14551,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14566,12 +14566,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14586,12 +14586,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>34781</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14601,12 +14601,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -14629,12 +14629,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>29107</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14679,12 +14679,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>22579</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>42491</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14899,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2023</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2023 (tasa de respuesta: 93,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -15698,12 +15698,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -15713,12 +15713,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -15776,12 +15776,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -15791,12 +15791,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -15924,12 +15924,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -15939,12 +15939,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -16002,12 +16002,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -16017,12 +16017,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16267,12 +16267,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>549</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -16282,12 +16282,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16302,12 +16302,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -16317,12 +16317,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>57,61%</t>
         </is>
       </c>
     </row>
@@ -16385,7 +16385,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -16415,12 +16415,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>542</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -16430,12 +16430,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>46,95%</t>
         </is>
       </c>
     </row>
@@ -16463,7 +16463,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -16528,12 +16528,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -16543,12 +16543,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -16606,12 +16606,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -16621,12 +16621,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -16641,12 +16641,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -16656,12 +16656,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>73,05%</t>
         </is>
       </c>
     </row>
@@ -16801,12 +16801,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>8019</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -16816,12 +16816,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -16871,12 +16871,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -16886,12 +16886,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -16949,12 +16949,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>858</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -16964,12 +16964,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -16984,12 +16984,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -16999,12 +16999,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -17027,12 +17027,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -17042,12 +17042,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -17062,12 +17062,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>468</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -17077,12 +17077,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -17097,12 +17097,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -17112,12 +17112,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -17140,12 +17140,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -17175,12 +17175,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -17190,12 +17190,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17210,12 +17210,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>15049</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -17225,12 +17225,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -17370,12 +17370,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -17385,12 +17385,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -17405,12 +17405,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>916</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -17420,12 +17420,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -17440,12 +17440,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -17455,12 +17455,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>46,31%</t>
         </is>
       </c>
     </row>
@@ -17488,7 +17488,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -17503,7 +17503,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -17518,12 +17518,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -17533,12 +17533,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -17553,12 +17553,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>594</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -17568,12 +17568,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -17601,7 +17601,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -17631,12 +17631,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>506</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -17646,12 +17646,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -17666,12 +17666,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>988</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -17681,12 +17681,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -17709,12 +17709,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -17744,12 +17744,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>828</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -17759,12 +17759,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -17779,12 +17779,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15642</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -17794,12 +17794,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,24%</t>
         </is>
       </c>
     </row>
@@ -17939,12 +17939,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -17954,12 +17954,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -17974,12 +17974,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -17989,12 +17989,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18009,12 +18009,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -18052,12 +18052,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -18067,12 +18067,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18087,12 +18087,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>362</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -18102,12 +18102,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18122,12 +18122,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -18137,12 +18137,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -18165,12 +18165,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -18180,12 +18180,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18200,12 +18200,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -18215,12 +18215,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -18235,12 +18235,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18250,12 +18250,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -18278,12 +18278,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -18293,12 +18293,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -18313,12 +18313,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -18328,12 +18328,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -18348,12 +18348,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>8878</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -18363,12 +18363,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -18508,12 +18508,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -18523,12 +18523,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -18543,12 +18543,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>326</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -18558,12 +18558,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -18578,12 +18578,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>325</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -18593,12 +18593,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -18621,12 +18621,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>452</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -18636,12 +18636,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -18656,12 +18656,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>890</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -18671,12 +18671,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -18691,12 +18691,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -18706,12 +18706,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>46,55%</t>
         </is>
       </c>
     </row>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -18769,12 +18769,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>430</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -18784,12 +18784,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>850</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -18819,12 +18819,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -18847,12 +18847,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -18862,12 +18862,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -18882,12 +18882,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -18897,12 +18897,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -18917,12 +18917,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -18932,12 +18932,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,34%</t>
         </is>
       </c>
     </row>
@@ -19077,12 +19077,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -19092,12 +19092,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -19112,12 +19112,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -19127,12 +19127,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -19147,12 +19147,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>31122</t>
+          <t>30813</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -19162,12 +19162,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -19190,12 +19190,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19205,12 +19205,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19225,12 +19225,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>14624</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19240,12 +19240,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>24649</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -19303,12 +19303,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19318,12 +19318,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19338,12 +19338,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -19353,12 +19353,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19373,12 +19373,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>26721</t>
+          <t>27776</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -19388,12 +19388,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -19431,12 +19431,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -19451,12 +19451,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>25636</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -19466,12 +19466,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -19486,12 +19486,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>33094</t>
+          <t>32955</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>50185</t>
+          <t>50269</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -19501,12 +19501,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q20C_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q20C_R-Edad-trans_orig.xlsx
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>65,34%</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>960</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>57,13%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>283</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>8613</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>63,06%</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>941</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>786</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>983</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>848</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>976</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>11941</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>63,7%</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,6%</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>920</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>62,02%</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>53,72%</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>21805</t>
+          <t>22150</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,12 +4914,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>18611</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>19041</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>31956</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>29500</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>47277</t>
+          <t>46883</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -5590,12 +5590,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>59,79%</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>49,79%</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6335,44 +6335,44 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>81,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3048</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4955</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>61,52%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3048</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4955</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>61,52%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>69,62%</t>
         </is>
       </c>
     </row>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6743,12 +6743,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>14851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>49,24%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>14148</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -7227,12 +7227,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15825</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20524</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -7340,12 +7340,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8626</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13365</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>73,69%</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8365,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>872</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>12312</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>58,02%</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>61,67%</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>18557</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>30575</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>23894</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>44475</t>
+          <t>44613</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>22023</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>36333</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22331</t>
+          <t>21699</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>21795</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>41296</t>
+          <t>43399</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>30236</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>38885</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>40272</t>
+          <t>39948</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>64152</t>
+          <t>63035</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>84,8%</t>
         </is>
       </c>
     </row>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>875</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>66,27%</t>
         </is>
       </c>
     </row>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -11558,12 +11558,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11573,12 +11573,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>821</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10424</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11643,12 +11643,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>63,77%</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>830</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>9825</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>56,66%</t>
         </is>
       </c>
     </row>
@@ -12014,12 +12014,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12029,12 +12029,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12049,12 +12049,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12064,12 +12064,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12099,12 +12099,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12177,12 +12177,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12212,12 +12212,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7777</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12633,12 +12633,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12653,12 +12653,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12711,12 +12711,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12766,12 +12766,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11920</t>
+          <t>11758</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12781,12 +12781,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12894,12 +12894,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>42,13%</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12972,12 +12972,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13007,12 +13007,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>45,86%</t>
         </is>
       </c>
     </row>
@@ -13157,7 +13157,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13187,12 +13187,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13202,12 +13202,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13222,12 +13222,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13237,12 +13237,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -13270,7 +13270,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13300,12 +13300,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13315,12 +13315,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13335,12 +13335,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>10039</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13350,12 +13350,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -13378,12 +13378,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13393,12 +13393,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13448,12 +13448,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>10017</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13463,12 +13463,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>47,9%</t>
         </is>
       </c>
     </row>
@@ -13496,7 +13496,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -13541,12 +13541,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11010</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13576,12 +13576,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -13726,7 +13726,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13889,7 +13889,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>793</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13919,12 +13919,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>51,7%</t>
         </is>
       </c>
     </row>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14065,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -14130,12 +14130,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14145,12 +14145,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -14290,12 +14290,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14305,12 +14305,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>23282</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>37717</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14375,12 +14375,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -14403,12 +14403,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14418,12 +14418,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>24998</t>
+          <t>24095</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14453,12 +14453,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>19716</t>
+          <t>18968</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>39251</t>
+          <t>38804</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14488,12 +14488,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -14516,12 +14516,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14531,12 +14531,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14551,12 +14551,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14566,12 +14566,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14586,12 +14586,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>34781</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14601,12 +14601,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -14629,12 +14629,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14679,12 +14679,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>22528</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>42242</t>
+          <t>41987</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -15668,12 +15668,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -15738,12 +15738,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>947</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -15816,12 +15816,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>947</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -15851,12 +15851,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -15894,12 +15894,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -15964,12 +15964,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -16042,12 +16042,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -16067,7 +16067,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -16077,12 +16077,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -16092,7 +16092,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -16110,17 +16110,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -16145,17 +16145,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -16180,17 +16180,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16262,32 +16262,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16297,32 +16297,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>50,45%</t>
         </is>
       </c>
     </row>
@@ -16340,7 +16340,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>940</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -16350,12 +16350,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -16365,7 +16365,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -16385,12 +16385,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -16410,32 +16410,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>548</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -16463,12 +16463,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>943</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -16498,12 +16498,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -16523,7 +16523,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -16533,12 +16533,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -16566,7 +16566,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -16576,12 +16576,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -16601,32 +16601,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -16636,32 +16636,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>71,93%</t>
         </is>
       </c>
     </row>
@@ -16679,17 +16679,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -16714,17 +16714,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -16749,17 +16749,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -16796,32 +16796,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>12313</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -16841,12 +16841,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -16866,32 +16866,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>14901</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>50,04%</t>
         </is>
       </c>
     </row>
@@ -16909,7 +16909,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -16919,12 +16919,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -16944,32 +16944,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -16979,32 +16979,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -17022,32 +17022,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -17057,32 +17057,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>470</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -17092,32 +17092,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -17135,32 +17135,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>8785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -17170,32 +17170,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17205,32 +17205,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -17248,17 +17248,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -17283,17 +17283,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>13033</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>13033</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>13033</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -17318,17 +17318,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>24437</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24437</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24437</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -17365,32 +17365,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -17400,32 +17400,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -17435,32 +17435,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -17478,7 +17478,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -17488,12 +17488,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -17503,7 +17503,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -17513,32 +17513,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -17548,32 +17548,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -17591,7 +17591,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>866</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -17601,12 +17601,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -17626,32 +17626,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -17661,32 +17661,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -17704,32 +17704,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -17739,32 +17739,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -17774,32 +17774,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15627</t>
+          <t>17393</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,24%</t>
         </is>
       </c>
     </row>
@@ -17817,17 +17817,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -17852,17 +17852,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -17887,17 +17887,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>25865</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>25865</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>25865</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -17934,32 +17934,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -17969,32 +17969,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18004,32 +18004,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -18047,32 +18047,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18082,32 +18082,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>364</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18117,32 +18117,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -18160,32 +18160,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18230,32 +18230,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>34,63%</t>
         </is>
       </c>
     </row>
@@ -18273,32 +18273,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -18308,32 +18308,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>562</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -18343,32 +18343,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8878</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -18386,17 +18386,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -18421,17 +18421,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -18456,17 +18456,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -18538,32 +18538,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>342</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -18573,32 +18573,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>345</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -18616,32 +18616,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>458</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -18651,32 +18651,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -18686,32 +18686,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>50,14%</t>
         </is>
       </c>
     </row>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -18764,32 +18764,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>424</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -18799,32 +18799,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>963</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -18842,32 +18842,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -18877,32 +18877,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -18912,32 +18912,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>62,97%</t>
         </is>
       </c>
     </row>
@@ -18955,17 +18955,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -18990,17 +18990,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -19025,17 +19025,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -19072,32 +19072,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -19107,32 +19107,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -19142,32 +19142,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>19951</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>30813</t>
+          <t>37767</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -19185,32 +19185,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19220,32 +19220,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>14624</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19255,32 +19255,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>24649</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -19298,32 +19298,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19333,32 +19333,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19368,32 +19368,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>29084</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -19411,32 +19411,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>29300</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -19446,32 +19446,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>19913</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -19481,32 +19481,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>41556</t>
+          <t>45361</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>32955</t>
+          <t>35425</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>50269</t>
+          <t>55003</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -19524,17 +19524,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -19559,17 +19559,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>43979</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>43979</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>43979</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -19594,17 +19594,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>100710</t>
+          <t>113520</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>100710</t>
+          <t>113520</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>100710</t>
+          <t>113520</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
